--- a/보험사_테이블_분류표_작업용.xlsx
+++ b/보험사_테이블_분류표_작업용.xlsx
@@ -649,8 +649,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + LNNO</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>월별 보험약관대출 마감 데이터</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -676,8 +685,17 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CTMNO + AP_NDDT + AP_STRDT</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>고객별 대출이력 및 연간/사업소득</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -703,8 +721,17 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>LNNO</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>대출 상세정보 원장</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -730,8 +757,17 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LNNO</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>대출 수납 원장. 잔여 대출금 확인 가능</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -865,8 +901,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>RCP_NV_SEQNO + RCP_YYMM</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>지급 마스터 테이블. 실제 테이블명 CCM_PY_RSLT_MSTR (CSV 오기)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -892,8 +937,17 @@
           <t>자동차계약</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CLS_YYMM + CVRCD</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>담보별 월별 자동차 발생손해액</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -919,8 +973,17 @@
           <t>자동차계약</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>자동차계약설계 정보 (한글명 오기: 자동차약관설계→자동차계약설계)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -946,8 +1009,17 @@
           <t>자동차계약</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + CVRCD + PLYNO</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>자동차보험료 분해</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -973,8 +1045,17 @@
           <t>자동차계약</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO + CVRCD</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>자동차보험 담보별 경과보험료</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1000,8 +1081,17 @@
           <t>자동차계약</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>갱신 전 계약 정보. 실제 테이블명 CLS_CR_RNWRT_CR (CSV 오기)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1054,8 +1144,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>휴면보험금 미지급금 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1243,8 +1342,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -1270,8 +1378,17 @@
           <t>공통관리</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>DCUNO</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>계약 관련 동의서 등 문서번호 관리</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="n">
@@ -1297,8 +1414,17 @@
           <t>공통관리</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + FR_LGIN_HMS</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>설계사 최초 로그인 시간 기록</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -1324,8 +1450,17 @@
           <t>공통관리</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>PRNOT_ITMCD</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>출력물 항목 코드 마스터</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="5" t="n">
@@ -1351,8 +1486,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>설계사(STFNO) 담당 영업가족고객 마스터. STFNO + BZ_FML_CTM_SEQNO → CTMNO 매핑</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -1378,8 +1522,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 추가정보</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="5" t="n">
@@ -1405,8 +1558,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 주소</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -1432,8 +1594,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 연락처</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="5" t="n">
@@ -1459,8 +1630,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 연락처 복본</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -1486,8 +1666,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 세대</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="5" t="n">
@@ -1513,8 +1702,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 이력계정</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -1540,8 +1738,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족 세대원 구성</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -1567,7 +1774,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -1601,7 +1812,7 @@
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 관련증권번호</t>
+          <t>CTMNO + CNN_PLYNO_OR_LLNO</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -1639,7 +1850,11 @@
           <t>고객상담/출력</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>CTMNO + CNS_DTHMS</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="16" customHeight="1">
@@ -1668,7 +1883,7 @@
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 동의시작일시 + 동의종료일시</t>
+          <t>CTMNO + AP_ND_DTHMS + SP_STR_DTHMS</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -1708,7 +1923,7 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 기준연월</t>
+          <t>CTMNO + ST_YYMM</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -1788,7 +2003,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 적용시작시점 + 적용종료시점</t>
+          <t>CTMNO + AP_ND_DTHMS + AP_STR_DTHMS</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -1908,7 +2123,7 @@
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 연락처오류처리구분코드</t>
+          <t>CTMNO + TLANO + TLTNO</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -1918,7 +2133,7 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>고객연락처 오류대상 처리</t>
+          <t>고객연락처 오류대상 처리 (전화지역번호+전화국번 기준)</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2163,7 @@
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 동의시작일시 + 동의종료일시</t>
+          <t>CTM_DSCNO + AD_ND_DTHMS + AP_STR_DTHMS</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -1958,7 +2173,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>고객정보동의 이력 관리 (이력 기준)</t>
+          <t>고객정보동의 이력 관리. CTMNO 아닌 CTM_DSCNO(고객식별번호) 기준</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2201,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr"/>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G48" s="14" t="inlineStr"/>
       <c r="H48" s="14" t="inlineStr">
         <is>
@@ -2020,7 +2239,7 @@
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 적용종료일자 + 적용시작일자</t>
+          <t>CTMNO + AP_NDDT + AP_STRDT</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -2060,7 +2279,7 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 적용시작일자 + 적용종료일자</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -2070,7 +2289,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>고객 직업 이력. 실제 테이블명: CUS_CTM_JB_CRR (CSV 오기)</t>
+          <t>없는 테이블 — DW 제외</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2357,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr"/>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G52" s="14" t="inlineStr"/>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -2251,8 +2474,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>ISNO</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>출력물 발급 이력. ISNO=출력물번호</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="10" t="n">
@@ -2280,7 +2512,7 @@
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>CTMNO + 이력구분코드 + 시작일자 + 종료일자</t>
+          <t>CTMNO + CRDIF_UTL_AGRE_FLGCD + AP_STR_DTHMS + AP_ND_DTHMS</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -2318,7 +2550,11 @@
           <t>고객동의/정보관리</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr"/>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G58" s="14" t="inlineStr"/>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2352,7 +2588,7 @@
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>가망고객번호 + 이력구분코드 + 시작일자 + 종료일자</t>
+          <t>CTMNO + CRDIF_UTL_AGRE_FLGCD + AP_STR_DTHMS + AP_ND_DTHMS</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -2392,7 +2628,7 @@
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>우편번호</t>
+          <t>PSTNO</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -2432,7 +2668,7 @@
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>우편번호ID + 기본주소구간ID</t>
+          <t>PSTNO_ID</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -2472,7 +2708,7 @@
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>우편번호</t>
+          <t>PSTNO</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -2512,7 +2748,7 @@
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>등기번호</t>
+          <t>RGSNO</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -2550,7 +2786,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F64" s="14" t="inlineStr"/>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G64" s="14" t="inlineStr"/>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2609,8 +2849,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>STFNO + BZ_FML_CTM_SEQNO</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>설계사 담당 영업가족고객 정보동의</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="5" t="n">
@@ -3041,7 +3290,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr">
         <is>
@@ -3100,7 +3353,11 @@
           <t>고객기본정보</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr"/>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G84" s="9" t="inlineStr"/>
       <c r="H84" s="9" t="inlineStr">
         <is>
@@ -3388,8 +3645,17 @@
           <t>계정원장</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>ACC_LDGNO</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>계정원장. 보험금 수납 경로 확인</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="5" t="n">
@@ -3415,8 +3681,17 @@
           <t>예금/방카</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>BNC_DP_LDGNO</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>방카슈랑스 예금원장</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -3442,8 +3717,17 @@
           <t>카드원장</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>CRD_LDGNO</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>카드 수납 예금원장</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="5" t="n">
@@ -3469,8 +3753,17 @@
           <t>예금/방카</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>DP_LDGNO</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>전체 예금원장. 계정/방카/카드 통합</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -3496,8 +3789,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>BZDY_ADM_DT</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>영업일 관리. 거의 미사용 — 도메인 재분류 필요(기타)</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="5" t="n">
@@ -3523,8 +3825,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>NP_ACC_LDGNO</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>미지급금 계정원장</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -3550,8 +3861,17 @@
           <t>수입보험료/수납</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>RV_SBNO</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>수납 대기건 정보</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="5" t="n">
@@ -3577,8 +3897,17 @@
           <t>지급</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>PY_CRNO</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>보험료 지급 발생 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -3604,8 +3933,17 @@
           <t>지급</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>DEB_DSCNO</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>지급정지건 정보</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="5" t="n">
@@ -3631,8 +3969,17 @@
           <t>전표</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>SLPNO</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>보험료 수납 발생 전표 정보</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -3658,8 +4005,17 @@
           <t>전표</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>SLPNO</t>
+        </is>
+      </c>
       <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>전표 상세 내역 (102 SLPNO 연결)</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="5" t="n">
@@ -3820,8 +4176,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>ATRCD</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>계약속성 메타 테이블 — 도메인 재분류 필요(기타)</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="5" t="n">
@@ -4738,8 +5103,17 @@
           <t>자동차기타</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="5" t="n">
@@ -4765,8 +5139,17 @@
           <t>자동차기타</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -4792,8 +5175,17 @@
           <t>자동차기타</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>CNMCD</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>차종명 코드 기준 자동차 정보 마스터</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="16" customHeight="1">
       <c r="A147" s="5" t="n">
@@ -4819,8 +5211,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>약관대출 가능금액 산정 — 도메인 재분류 필요(약관대출)</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="16" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -4873,8 +5274,17 @@
           <t>일반보험계약</t>
         </is>
       </c>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CLS_YYMM</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>일반보험 사고담보 마감</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -4900,8 +5310,17 @@
           <t>일반보험계약</t>
         </is>
       </c>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>일반보험계약담보 산출</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="5" t="n">
@@ -4927,8 +5346,17 @@
           <t>일반보험계약</t>
         </is>
       </c>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>일반보험 재사고계약 마감</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -4954,8 +5382,17 @@
           <t>일반보험계약</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>일반보험 잠재수익 기초자료</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="5" t="n">
@@ -5062,8 +5499,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>증번 기준 공동인수 정보 및 지분율</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="5" t="n">
@@ -5089,8 +5535,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>ATRCD</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>계약속성 코드 테이블 — 도메인 재분류 필요(기타)</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -5116,8 +5571,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>계약 유의승환 정보. 한글명 오기(계약의승한채세→계약유의승환상세)</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="5" t="n">
@@ -5143,8 +5607,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + RELPC_TPCD + NDS_AP_ND_DTHMS + NDS_AP_STR_DTHMS</t>
+        </is>
+      </c>
       <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>계약관계자. 테이블명/한글명 오기(INS_CR_AD/보험계약보험자→INS_CR_RELPC/계약관계자)</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="2" t="n">
@@ -5170,8 +5643,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F160" s="4" t="inlineStr"/>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + NDS_AP_ND_DTHMS + NDS_AP_STR_DTHMS</t>
+        </is>
+      </c>
       <c r="G160" s="4" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>계약자동차정보. 한글명 오기(계약자동처지정보→계약자동차정보)</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="5" t="n">
@@ -5197,8 +5679,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + DH_STF_TPCD + NDS_AP_ND_DTHMS + NDS_AP_STR_DTHMS</t>
+        </is>
+      </c>
       <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>계약담당직원이력</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="2" t="n">
@@ -5224,8 +5715,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F162" s="4" t="inlineStr"/>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G162" s="4" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>없는 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="5" t="n">
@@ -5251,8 +5751,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G163" s="4" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>자동차 마일리지 정산결과 정보. 한글명 오기(계약하자리자청산→자동차마일리지정산결과)</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="2" t="n">
@@ -5278,8 +5787,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr"/>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + ATRCD</t>
+        </is>
+      </c>
       <c r="G164" s="4" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>계약배서 상세. 한글명 오기(계약배서마감→계약배서상세)</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="5" t="n">
@@ -5305,8 +5823,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + NDSNO</t>
+        </is>
+      </c>
       <c r="G165" s="4" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>계약배서 마스터</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="2" t="n">
@@ -5332,8 +5859,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + OJ_SEQNO</t>
+        </is>
+      </c>
       <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>계약목적물. 테이블명/한글명 오기(INS_CR_OI/승인→INS_CR_OJ/계약목적물)</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="5" t="n">
@@ -5359,8 +5895,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + AP_NDDT</t>
+        </is>
+      </c>
       <c r="G167" s="4" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>계약지급제한</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="2" t="n">
@@ -5386,8 +5931,17 @@
           <t>계약관계자</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr"/>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>CTMNO + PLYNO + RELPC_SEQNO</t>
+        </is>
+      </c>
       <c r="G168" s="4" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>계약관계자 주소이력</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="5" t="n">
@@ -5413,8 +5967,17 @@
           <t>계약관계자</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + RELPC_RELCD</t>
+        </is>
+      </c>
       <c r="G169" s="4" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>계약관계자 관계</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="2" t="n">
@@ -5440,8 +6003,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr"/>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G170" s="4" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>없는 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="16" customHeight="1">
       <c r="A171" s="5" t="n">
@@ -5467,8 +6039,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F171" s="4" t="inlineStr"/>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + AP_NDDT + AP_STRDT</t>
+        </is>
+      </c>
       <c r="G171" s="4" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>계약갱신관리. 한글명 오기(자동이체자사용료→계약갱신관리)</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="2" t="n">
@@ -5494,8 +6075,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr"/>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>CARNO</t>
+        </is>
+      </c>
       <c r="G172" s="4" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>자동차 자사요율. 한글명 오기(계약상담이력→자동차자사요율)</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="5" t="n">
@@ -5521,8 +6111,17 @@
           <t>일반계약</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr"/>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CR_STCD</t>
+        </is>
+      </c>
       <c r="G173" s="4" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>계약상태이력</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="2" t="n">
@@ -5791,8 +6390,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F183" s="4" t="inlineStr"/>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CLS_YYMM + DU_AR_FLGCD</t>
+        </is>
+      </c>
       <c r="G183" s="4" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>보험료 확정건 정보</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="2" t="n">
@@ -6250,8 +6858,17 @@
           <t>수입보험료/수납</t>
         </is>
       </c>
-      <c r="F200" s="4" t="inlineStr"/>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + INCM_RPM_CR_SEQNO</t>
+        </is>
+      </c>
       <c r="G200" s="4" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>보험료 납입 상세 (매출 테이블)</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="5" t="n">
@@ -6412,8 +7029,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F206" s="4" t="inlineStr"/>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + CVRCD + PLYNO</t>
+        </is>
+      </c>
       <c r="G206" s="4" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>해약환급금·경과보험료·대출가능금액 산출</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="5" t="n">
@@ -6574,8 +7200,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F212" s="4" t="inlineStr"/>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + NDSNO</t>
+        </is>
+      </c>
       <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>중도인출금 분할지급 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="5" t="n">
@@ -6979,8 +7614,17 @@
           <t>지급</t>
         </is>
       </c>
-      <c r="F227" s="4" t="inlineStr"/>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + RCP_NV_SEQNO + RCP_YYMM + CMP_PY_RLTNO</t>
+        </is>
+      </c>
       <c r="G227" s="4" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>보상 지급 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="16" customHeight="1">
       <c r="A228" s="2" t="n">
@@ -7438,8 +8082,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F244" s="4" t="inlineStr"/>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>UTATP_DSCNO</t>
+        </is>
+      </c>
       <c r="G244" s="4" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>인수유의자 테이블 (한글명 오기: 제지급대상 아님)</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="16" customHeight="1">
       <c r="A245" s="5" t="n">
@@ -7465,8 +8118,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F245" s="4" t="inlineStr"/>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>제지급대상. 실손전환 중지 여부 판단 시 사용 (한글명 오기)</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="16" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -7492,8 +8154,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F246" s="4" t="inlineStr"/>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G246" s="4" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>정산통지 관계사 순번 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="16" customHeight="1">
       <c r="A247" s="5" t="n">
@@ -7843,8 +8514,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F259" s="4" t="inlineStr"/>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CLM_NV_SEQNO + CR_CVRCD</t>
+        </is>
+      </c>
       <c r="G259" s="4" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>추산지급 계약정보. 입통원 관련 (한글명 오기: 주산→추산)</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="2" t="n">
@@ -7870,8 +8550,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F260" s="4" t="inlineStr"/>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>CLMPS_SEQNO + RCP_NV_SEQNO + RCP_YYMM</t>
+        </is>
+      </c>
       <c r="G260" s="4" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>추산지급 테이블 (한글명 오기: 주산→추산)</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="16" customHeight="1">
       <c r="A261" s="5" t="n">
@@ -7897,8 +8586,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F261" s="4" t="inlineStr"/>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>CLMPS_SEQNO + RCP_NV_SEQNO + RCP_YYMM + PLYNO + CC_SEQ</t>
+        </is>
+      </c>
       <c r="G261" s="4" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>추산지급 내역. 지급금액 및 내역 (한글명 오기: 주산→추산)</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="16" customHeight="1">
       <c r="A262" s="2" t="n">
@@ -8059,8 +8757,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F267" s="4" t="inlineStr"/>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G267" s="4" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>부보차량 정보 (월별 증권 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="16" customHeight="1">
       <c r="A268" s="2" t="n">
@@ -8140,8 +8847,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F270" s="4" t="inlineStr"/>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO + INCM_PRM_CR_SEQNO</t>
+        </is>
+      </c>
       <c r="G270" s="4" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>자동차보험 수입보험료 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="16" customHeight="1">
       <c r="A271" s="5" t="n">
@@ -8194,8 +8910,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F272" s="4" t="inlineStr"/>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G272" s="4" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>증권 기준 자동차 갱신 횟수</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="16" customHeight="1">
       <c r="A273" s="5" t="n">
@@ -8221,8 +8946,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F273" s="4" t="inlineStr"/>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G273" s="4" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>자동차 갱신대상 만기계약. 만기월 기준 갱신 미계약</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="16" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -8248,8 +8982,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F274" s="4" t="inlineStr"/>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G274" s="4" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>당월 갱신 예상 증번 (자동차 갱신대상 계약)</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="16" customHeight="1">
       <c r="A275" s="5" t="n">
@@ -8275,8 +9018,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F275" s="4" t="inlineStr"/>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G275" s="4" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="16" customHeight="1">
       <c r="A276" s="2" t="n">
@@ -8302,8 +9054,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F276" s="4" t="inlineStr"/>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G276" s="4" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>최초 자동차보험 가입 시점의 계약 정보</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="5" t="n">
@@ -8329,8 +9090,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F277" s="4" t="inlineStr"/>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CVRCD</t>
+        </is>
+      </c>
       <c r="G277" s="4" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>월별 자동차보험 통계자료</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="2" t="n">
@@ -8356,8 +9126,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F278" s="4" t="inlineStr"/>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G278" s="4" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>월별 자동차 정보. 주로 신규갱신구분코드 확인용</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="16" customHeight="1">
       <c r="A279" s="5" t="n">
@@ -8383,8 +9162,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F279" s="4" t="inlineStr"/>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO</t>
+        </is>
+      </c>
       <c r="G279" s="4" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>월별 자동차보험 메인 테이블. 실제 테이블명 M_CCR_MTHY_CR_INS_CR (CSV 오기)</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="16" customHeight="1">
       <c r="A280" s="2" t="n">
@@ -8410,8 +9198,17 @@
           <t>자동차월별통계</t>
         </is>
       </c>
-      <c r="F280" s="4" t="inlineStr"/>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + CVRCD + PLYNO</t>
+        </is>
+      </c>
       <c r="G280" s="4" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>월별 자동차보험 통계자료. 경과 원수보험료 기반 손해율 계산용</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="16" customHeight="1">
       <c r="A281" s="5" t="n">
@@ -8518,8 +9315,17 @@
           <t>자동차사고현황</t>
         </is>
       </c>
-      <c r="F284" s="4" t="inlineStr"/>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + RCP_YYMM + RCP_NV_SEQNO + CLM_CVRCD</t>
+        </is>
+      </c>
       <c r="G284" s="4" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>자동차 보상발생 테이블. 증권별 담보 보상 발생 시 기록</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="16" customHeight="1">
       <c r="A285" s="5" t="n">
@@ -8545,8 +9351,17 @@
           <t>자동차사고현황</t>
         </is>
       </c>
-      <c r="F285" s="4" t="inlineStr"/>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>RCP_NV_SEQNO + RCP_YYMM + CLM_CVRCD</t>
+        </is>
+      </c>
       <c r="G285" s="4" t="inlineStr"/>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>자동차 보상면책 테이블. 피해서열 확인용</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -8572,8 +9387,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F286" s="4" t="inlineStr"/>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + RCP_YYMM + RCP_NV_SEQNO</t>
+        </is>
+      </c>
       <c r="G286" s="4" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>보상사고 발생 마스터 (한글명 오기)</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="5" t="n">
@@ -8734,8 +9558,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F292" s="4" t="inlineStr"/>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G292" s="4" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="16" customHeight="1">
       <c r="A293" s="5" t="n">
@@ -8761,8 +9594,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F293" s="4" t="inlineStr"/>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G293" s="4" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="16" customHeight="1">
       <c r="A294" s="2" t="n">
@@ -8788,8 +9630,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F294" s="4" t="inlineStr"/>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G294" s="4" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="16" customHeight="1">
       <c r="A295" s="5" t="n">
@@ -8815,8 +9666,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F295" s="4" t="inlineStr"/>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G295" s="4" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="16" customHeight="1">
       <c r="A296" s="2" t="n">
@@ -8842,8 +9702,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F296" s="4" t="inlineStr"/>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G296" s="4" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="5" t="n">
@@ -8869,8 +9738,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F297" s="4" t="inlineStr"/>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G297" s="4" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="16" customHeight="1">
       <c r="A298" s="2" t="n">
@@ -8896,8 +9774,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F298" s="4" t="inlineStr"/>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G298" s="4" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="16" customHeight="1">
       <c r="A299" s="5" t="n">
@@ -8923,8 +9810,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F299" s="4" t="inlineStr"/>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G299" s="4" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="16" customHeight="1">
       <c r="A300" s="2" t="n">
@@ -8950,8 +9846,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F300" s="4" t="inlineStr"/>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G300" s="4" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="16" customHeight="1">
       <c r="A301" s="5" t="n">
@@ -8977,8 +9882,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F301" s="4" t="inlineStr"/>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G301" s="4" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="2" t="n">
@@ -9004,8 +9918,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F302" s="4" t="inlineStr"/>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G302" s="4" t="inlineStr"/>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="16" customHeight="1">
       <c r="A303" s="5" t="n">
@@ -9031,8 +9954,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F303" s="4" t="inlineStr"/>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G303" s="4" t="inlineStr"/>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="16" customHeight="1">
       <c r="A304" s="2" t="n">
@@ -9058,8 +9990,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F304" s="4" t="inlineStr"/>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G304" s="4" t="inlineStr"/>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="16" customHeight="1">
       <c r="A305" s="5" t="n">
@@ -9085,8 +10026,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F305" s="4" t="inlineStr"/>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G305" s="4" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="16" customHeight="1">
       <c r="A306" s="2" t="n">
@@ -9112,8 +10062,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F306" s="4" t="inlineStr"/>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G306" s="4" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="16" customHeight="1">
       <c r="A307" s="5" t="n">
@@ -9139,8 +10098,17 @@
           <t>담보</t>
         </is>
       </c>
-      <c r="F307" s="4" t="inlineStr"/>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G307" s="4" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="16" customHeight="1">
       <c r="A308" s="2" t="n">
@@ -9166,8 +10134,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F308" s="4" t="inlineStr"/>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G308" s="4" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="16" customHeight="1">
       <c r="A309" s="5" t="n">
@@ -9193,8 +10170,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F309" s="4" t="inlineStr"/>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G309" s="4" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="16" customHeight="1">
       <c r="A310" s="2" t="n">
@@ -9220,8 +10206,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F310" s="4" t="inlineStr"/>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G310" s="4" t="inlineStr"/>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="16" customHeight="1">
       <c r="A311" s="5" t="n">
@@ -9247,8 +10242,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F311" s="4" t="inlineStr"/>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G311" s="4" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="16" customHeight="1">
       <c r="A312" s="2" t="n">
@@ -9274,8 +10278,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F312" s="4" t="inlineStr"/>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G312" s="4" t="inlineStr"/>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="16" customHeight="1">
       <c r="A313" s="5" t="n">
@@ -9301,8 +10314,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F313" s="4" t="inlineStr"/>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G313" s="4" t="inlineStr"/>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="16" customHeight="1">
       <c r="A314" s="2" t="n">
@@ -9328,8 +10350,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F314" s="4" t="inlineStr"/>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G314" s="4" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="16" customHeight="1">
       <c r="A315" s="5" t="n">
@@ -9355,8 +10386,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F315" s="4" t="inlineStr"/>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G315" s="4" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="16" customHeight="1">
       <c r="A316" s="2" t="n">
@@ -9382,8 +10422,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F316" s="4" t="inlineStr"/>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G316" s="4" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="16" customHeight="1">
       <c r="A317" s="5" t="n">
@@ -9409,8 +10458,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F317" s="4" t="inlineStr"/>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G317" s="4" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="16" customHeight="1">
       <c r="A318" s="2" t="n">
@@ -9436,8 +10494,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F318" s="4" t="inlineStr"/>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G318" s="4" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="16" customHeight="1">
       <c r="A319" s="5" t="n">
@@ -9463,8 +10530,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F319" s="4" t="inlineStr"/>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G319" s="4" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="16" customHeight="1">
       <c r="A320" s="2" t="n">
@@ -9490,8 +10566,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F320" s="4" t="inlineStr"/>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G320" s="4" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="16" customHeight="1">
       <c r="A321" s="5" t="n">
@@ -9517,8 +10602,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F321" s="4" t="inlineStr"/>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G321" s="4" t="inlineStr"/>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="16" customHeight="1">
       <c r="A322" s="2" t="n">
@@ -9544,8 +10638,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F322" s="4" t="inlineStr"/>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G322" s="4" t="inlineStr"/>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="16" customHeight="1">
       <c r="A323" s="5" t="n">
@@ -9571,8 +10674,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F323" s="4" t="inlineStr"/>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G323" s="4" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="16" customHeight="1">
       <c r="A324" s="2" t="n">
@@ -9598,8 +10710,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F324" s="4" t="inlineStr"/>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G324" s="4" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="16" customHeight="1">
       <c r="A325" s="5" t="n">
@@ -9625,8 +10746,17 @@
           <t>상품기본</t>
         </is>
       </c>
-      <c r="F325" s="4" t="inlineStr"/>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G325" s="4" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="16" customHeight="1">
       <c r="A326" s="2" t="n">
@@ -9652,8 +10782,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F326" s="4" t="inlineStr"/>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G326" s="4" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="16" customHeight="1">
       <c r="A327" s="5" t="n">
@@ -9679,8 +10818,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F327" s="4" t="inlineStr"/>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G327" s="4" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="16" customHeight="1">
       <c r="A328" s="2" t="n">
@@ -9706,8 +10854,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F328" s="4" t="inlineStr"/>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G328" s="4" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="16" customHeight="1">
       <c r="A329" s="5" t="n">
@@ -9733,8 +10890,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F329" s="4" t="inlineStr"/>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G329" s="4" t="inlineStr"/>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="16" customHeight="1">
       <c r="A330" s="2" t="n">
@@ -9760,8 +10926,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F330" s="4" t="inlineStr"/>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G330" s="4" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="16" customHeight="1">
       <c r="A331" s="5" t="n">
@@ -9787,8 +10962,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F331" s="4" t="inlineStr"/>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G331" s="4" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="16" customHeight="1">
       <c r="A332" s="2" t="n">
@@ -9814,8 +10998,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F332" s="4" t="inlineStr"/>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G332" s="4" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="16" customHeight="1">
       <c r="A333" s="5" t="n">
@@ -9841,8 +11034,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F333" s="4" t="inlineStr"/>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G333" s="4" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="16" customHeight="1">
       <c r="A334" s="2" t="n">
@@ -9868,8 +11070,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F334" s="4" t="inlineStr"/>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G334" s="4" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="16" customHeight="1">
       <c r="A335" s="5" t="n">
@@ -9895,8 +11106,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F335" s="4" t="inlineStr"/>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G335" s="4" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="16" customHeight="1">
       <c r="A336" s="2" t="n">
@@ -9922,8 +11142,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F336" s="4" t="inlineStr"/>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G336" s="4" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="16" customHeight="1">
       <c r="A337" s="5" t="n">
@@ -9949,8 +11178,17 @@
           <t>SFA기타</t>
         </is>
       </c>
-      <c r="F337" s="4" t="inlineStr"/>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G337" s="4" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="16" customHeight="1">
       <c r="A338" s="2" t="n">
@@ -9976,8 +11214,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F338" s="4" t="inlineStr"/>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G338" s="4" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="16" customHeight="1">
       <c r="A339" s="5" t="n">
@@ -10003,8 +11250,17 @@
           <t>CMS캠페인</t>
         </is>
       </c>
-      <c r="F339" s="4" t="inlineStr"/>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G339" s="4" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="16" customHeight="1">
       <c r="A340" s="2" t="n">
@@ -10248,7 +11504,7 @@
       </c>
       <c r="F348" s="12" t="inlineStr">
         <is>
-          <t>신용정보원증권번호</t>
+          <t>CRDIS_PLYNO</t>
         </is>
       </c>
       <c r="G348" s="12" t="inlineStr">
@@ -10288,7 +11544,7 @@
       </c>
       <c r="F349" s="12" t="inlineStr">
         <is>
-          <t>CLS_YYMM + 고객번호</t>
+          <t>CLS_YYMM + CTMNO</t>
         </is>
       </c>
       <c r="G349" s="12" t="inlineStr">
@@ -10328,7 +11584,7 @@
       </c>
       <c r="F350" s="12" t="inlineStr">
         <is>
-          <t>CLS_YYMM + 고객번호</t>
+          <t>CLS_YYMM + CTMNO</t>
         </is>
       </c>
       <c r="G350" s="12" t="inlineStr">
@@ -10420,8 +11676,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F353" s="4" t="inlineStr"/>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G353" s="4" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="16" customHeight="1">
       <c r="A354" s="2" t="n">
@@ -11151,7 +12416,7 @@
       </c>
       <c r="F380" s="12" t="inlineStr">
         <is>
-          <t>CLS_YYMM + 고객번호</t>
+          <t>CLS_YYMM + CTMNO</t>
         </is>
       </c>
       <c r="G380" s="12" t="inlineStr">
@@ -11862,8 +13127,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F404" s="4" t="inlineStr"/>
+      <c r="F404" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO + INCM_PRM_CR_SEQNO</t>
+        </is>
+      </c>
       <c r="G404" s="4" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>일반보험 수입보험료 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="16" customHeight="1">
       <c r="A405" s="5" t="n">
@@ -12186,8 +13460,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F416" s="4" t="inlineStr"/>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>CLS_YYMM + PLYNO + INCM_PRM_CR_SEQNO</t>
+        </is>
+      </c>
       <c r="G416" s="4" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>장기보험 수입보험료 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="16" customHeight="1">
       <c r="A417" s="5" t="n">
@@ -12321,8 +13604,17 @@
           <t>재무기타</t>
         </is>
       </c>
-      <c r="F421" s="4" t="inlineStr"/>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO + CGAF_CH_SEQNO + RELPC_SEQNO</t>
+        </is>
+      </c>
       <c r="G421" s="4" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>장기심사신청 원지급 상세. 설계 시점 신정원 조회 시 입원/수술이력</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="16" customHeight="1">
       <c r="A422" s="2" t="n">
@@ -14642,8 +15934,17 @@
           <t>고객주소/연락처</t>
         </is>
       </c>
-      <c r="F506" s="4" t="inlineStr"/>
+      <c r="F506" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G506" s="4" t="inlineStr"/>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>실제 테이블명 SFA_BZ_FML_CTM_ADR_CH (CSV 오기). 미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="5" t="n">
@@ -14669,8 +15970,17 @@
           <t>영업가족고객</t>
         </is>
       </c>
-      <c r="F507" s="4" t="inlineStr"/>
+      <c r="F507" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G507" s="4" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="16" customHeight="1">
       <c r="A508" s="2" t="n">
@@ -16370,8 +17680,17 @@
           <t>고객동의/정보관리</t>
         </is>
       </c>
-      <c r="F570" s="4" t="inlineStr"/>
+      <c r="F570" s="4" t="inlineStr">
+        <is>
+          <t>SFP_CTMNO + AP_NDDY_CITY + AP_STRDY_CITY</t>
+        </is>
+      </c>
       <c r="G570" s="4" t="inlineStr"/>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>SFP 등록고객 신용정보활동동의 이력</t>
+        </is>
+      </c>
     </row>
     <row r="571" ht="16" customHeight="1">
       <c r="A571" s="5" t="n">
@@ -16987,8 +18306,17 @@
           <t>코드/마스터</t>
         </is>
       </c>
-      <c r="F593" s="4" t="inlineStr"/>
+      <c r="F593" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G593" s="4" t="inlineStr"/>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="594" ht="16" customHeight="1">
       <c r="A594" s="2" t="n">
@@ -17095,8 +18423,17 @@
           <t>시스템/웹</t>
         </is>
       </c>
-      <c r="F597" s="4" t="inlineStr"/>
+      <c r="F597" s="4" t="inlineStr">
+        <is>
+          <t>CUID</t>
+        </is>
+      </c>
       <c r="G597" s="4" t="inlineStr"/>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>푸쉬 서비스 사용자 정보 (앱 고객 아이디 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="598" ht="16" customHeight="1">
       <c r="A598" s="2" t="n">
@@ -17122,8 +18459,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F598" s="4" t="inlineStr"/>
+      <c r="F598" s="4" t="inlineStr">
+        <is>
+          <t>POLNO</t>
+        </is>
+      </c>
       <c r="G598" s="4" t="inlineStr"/>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>자동설계 보험료 산출 결과 관리</t>
+        </is>
+      </c>
     </row>
     <row r="599" ht="16" customHeight="1">
       <c r="A599" s="5" t="n">
@@ -17149,8 +18495,17 @@
           <t>상담/콜이력</t>
         </is>
       </c>
-      <c r="F599" s="4" t="inlineStr"/>
+      <c r="F599" s="4" t="inlineStr">
+        <is>
+          <t>LISTID + CUSTID + LISTSEQID</t>
+        </is>
+      </c>
       <c r="G599" s="4" t="inlineStr"/>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>TM 상담 전화 로그. CUSTID 기준 고객 접촉 기록</t>
+        </is>
+      </c>
     </row>
     <row r="600" ht="16" customHeight="1">
       <c r="A600" s="2" t="n">
@@ -17176,8 +18531,17 @@
           <t>상담/콜이력</t>
         </is>
       </c>
-      <c r="F600" s="4" t="inlineStr"/>
+      <c r="F600" s="4" t="inlineStr">
+        <is>
+          <t>CALLID</t>
+        </is>
+      </c>
       <c r="G600" s="4" t="inlineStr"/>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>콜 상세 상담 이력. CALLID 기준</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="16" customHeight="1">
       <c r="A601" s="5" t="n">
@@ -17203,8 +18567,17 @@
           <t>상담/콜이력</t>
         </is>
       </c>
-      <c r="F601" s="4" t="inlineStr"/>
+      <c r="F601" s="4" t="inlineStr">
+        <is>
+          <t>CALLID</t>
+        </is>
+      </c>
       <c r="G601" s="4" t="inlineStr"/>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>콜 이력. TB_CNSLT_DTHIST(599)와 CALLID로 연결</t>
+        </is>
+      </c>
     </row>
     <row r="602" ht="16" customHeight="1">
       <c r="A602" s="2" t="n">
@@ -17230,8 +18603,17 @@
           <t>상담/콜이력</t>
         </is>
       </c>
-      <c r="F602" s="4" t="inlineStr"/>
+      <c r="F602" s="4" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
       <c r="G602" s="4" t="inlineStr"/>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>상담유형 코드 마스터. TB_CNSLT_DTHIST와 연결</t>
+        </is>
+      </c>
     </row>
     <row r="603" ht="16" customHeight="1">
       <c r="A603" s="5" t="n">
@@ -17257,8 +18639,17 @@
           <t>코드/마스터</t>
         </is>
       </c>
-      <c r="F603" s="4" t="inlineStr"/>
+      <c r="F603" s="4" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
       <c r="G603" s="4" t="inlineStr"/>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>TM 영역 공통 코드북</t>
+        </is>
+      </c>
     </row>
     <row r="604" ht="16" customHeight="1">
       <c r="A604" s="2" t="n">
@@ -17391,8 +18782,17 @@
           <t>고객동의/정보관리</t>
         </is>
       </c>
-      <c r="F607" s="4" t="inlineStr"/>
+      <c r="F607" s="4" t="inlineStr">
+        <is>
+          <t>CUSTID + AP_ND_DTHMS + AP_STR_DTHMS</t>
+        </is>
+      </c>
       <c r="G607" s="4" t="inlineStr"/>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>TM 고객 신용정보활동동의 이력 관리 (CUSTID 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="608" ht="16" customHeight="1">
       <c r="A608" s="10" t="n">
@@ -17458,8 +18858,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F609" s="4" t="inlineStr"/>
+      <c r="F609" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO</t>
+        </is>
+      </c>
       <c r="G609" s="4" t="inlineStr"/>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>TM 계약 취급자 이관신청 이력 관리. 한글명 정정: 취급자이관신청 (CSV 오기: 하자자여신청)</t>
+        </is>
+      </c>
     </row>
     <row r="610" ht="16" customHeight="1">
       <c r="A610" s="2" t="n">
@@ -17485,8 +18894,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F610" s="4" t="inlineStr"/>
+      <c r="F610" s="4" t="inlineStr">
+        <is>
+          <t>CARNO_OR_CHSNO</t>
+        </is>
+      </c>
       <c r="G610" s="4" t="inlineStr"/>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>제휴처별 유입정보를 TM 자동차에 매핑. 이지세이브 차량/차대번호 기준</t>
+        </is>
+      </c>
     </row>
     <row r="611" ht="16" customHeight="1">
       <c r="A611" s="5" t="n">
@@ -17539,8 +18957,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F612" s="4" t="inlineStr"/>
+      <c r="F612" s="4" t="inlineStr">
+        <is>
+          <t>CUSTID</t>
+        </is>
+      </c>
       <c r="G612" s="4" t="inlineStr"/>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>TM 채널 고객 유입시점 정보 (CUSTID 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="613" ht="16" customHeight="1">
       <c r="A613" s="5" t="n">
@@ -17566,8 +18993,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F613" s="4" t="inlineStr"/>
+      <c r="F613" s="4" t="inlineStr">
+        <is>
+          <t>CUSTID</t>
+        </is>
+      </c>
       <c r="G613" s="4" t="inlineStr"/>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>TM 고객 동의 관리. 주로 동의거절 확인용</t>
+        </is>
+      </c>
     </row>
     <row r="614" ht="16" customHeight="1">
       <c r="A614" s="2" t="n">
@@ -17809,8 +19245,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F622" s="4" t="inlineStr"/>
+      <c r="F622" s="4" t="inlineStr">
+        <is>
+          <t>CUSTID</t>
+        </is>
+      </c>
       <c r="G622" s="4" t="inlineStr"/>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>상담 스케줄 예약고객 조회용</t>
+        </is>
+      </c>
     </row>
     <row r="623" ht="16" customHeight="1">
       <c r="A623" s="5" t="n">
@@ -17890,8 +19335,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F625" s="4" t="inlineStr"/>
+      <c r="F625" s="4" t="inlineStr">
+        <is>
+          <t>USERID</t>
+        </is>
+      </c>
       <c r="G625" s="4" t="inlineStr"/>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>TM 사용자 마스터 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="16" customHeight="1">
       <c r="A626" s="2" t="n">
@@ -17944,8 +19398,17 @@
           <t>VOC</t>
         </is>
       </c>
-      <c r="F627" s="4" t="inlineStr"/>
+      <c r="F627" s="4" t="inlineStr">
+        <is>
+          <t>ID_VOC</t>
+        </is>
+      </c>
       <c r="G627" s="4" t="inlineStr"/>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>VOC 아이디 기준 마스터</t>
+        </is>
+      </c>
     </row>
     <row r="628" ht="16" customHeight="1">
       <c r="A628" s="2" t="n">
@@ -17998,8 +19461,17 @@
           <t>VOC</t>
         </is>
       </c>
-      <c r="F629" s="4" t="inlineStr"/>
+      <c r="F629" s="4" t="inlineStr">
+        <is>
+          <t>ID_VOC</t>
+        </is>
+      </c>
       <c r="G629" s="4" t="inlineStr"/>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>VOC별 처리결과 적재</t>
+        </is>
+      </c>
     </row>
     <row r="630" ht="16" customHeight="1">
       <c r="A630" s="2" t="n">
@@ -18025,8 +19497,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F630" s="4" t="inlineStr"/>
+      <c r="F630" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G630" s="4" t="inlineStr"/>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="631" ht="16" customHeight="1">
       <c r="A631" s="5" t="n">
@@ -18052,8 +19533,17 @@
           <t>CRM기타</t>
         </is>
       </c>
-      <c r="F631" s="4" t="inlineStr"/>
+      <c r="F631" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G631" s="4" t="inlineStr"/>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>CMS 테이블 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="632" ht="16" customHeight="1">
       <c r="A632" s="2" t="n">
@@ -18106,8 +19596,17 @@
           <t>공통기타</t>
         </is>
       </c>
-      <c r="F633" s="4" t="inlineStr"/>
+      <c r="F633" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G633" s="4" t="inlineStr"/>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>2018~2019년 아파트 실거래가 데이터. 현재 미사용 — DW 제외</t>
+        </is>
+      </c>
     </row>
     <row r="634" ht="16" customHeight="1">
       <c r="A634" s="2" t="n">
@@ -18187,8 +19686,17 @@
           <t>시스템/웹</t>
         </is>
       </c>
-      <c r="F636" s="4" t="inlineStr"/>
+      <c r="F636" s="4" t="inlineStr">
+        <is>
+          <t>CTM_KEY</t>
+        </is>
+      </c>
       <c r="G636" s="4" t="inlineStr"/>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>이벤트 유입고객 관리 테이블</t>
+        </is>
+      </c>
     </row>
     <row r="637" ht="16" customHeight="1">
       <c r="A637" s="10" t="n">
@@ -18216,7 +19724,7 @@
       </c>
       <c r="F637" s="12" t="inlineStr">
         <is>
-          <t>고객번호</t>
+          <t>CTMNO</t>
         </is>
       </c>
       <c r="G637" s="12" t="inlineStr">
@@ -18254,8 +19762,17 @@
           <t>시스템/웹</t>
         </is>
       </c>
-      <c r="F638" s="4" t="inlineStr"/>
+      <c r="F638" s="4" t="inlineStr">
+        <is>
+          <t>CTMNO</t>
+        </is>
+      </c>
       <c r="G638" s="4" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>웹 로그인 고객 이력 (CTMNO 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="639" ht="16" customHeight="1">
       <c r="A639" s="5" t="n">
@@ -18281,8 +19798,17 @@
           <t>자동차기타</t>
         </is>
       </c>
-      <c r="F639" s="4" t="inlineStr"/>
+      <c r="F639" s="4" t="inlineStr">
+        <is>
+          <t>PLYNO_OR_LNNO</t>
+        </is>
+      </c>
       <c r="G639" s="4" t="inlineStr"/>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>소액결제 동의 테이블. 자동차보험과 무관 — 도메인 재분류 필요</t>
+        </is>
+      </c>
     </row>
     <row r="640" ht="16" customHeight="1">
       <c r="A640" s="2" t="n">
@@ -18308,8 +19834,17 @@
           <t>공통관리</t>
         </is>
       </c>
-      <c r="F640" s="4" t="inlineStr"/>
+      <c r="F640" s="4" t="inlineStr">
+        <is>
+          <t>ECRE_NO</t>
+        </is>
+      </c>
       <c r="G640" s="4" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>알림톡 발송 이력. ECRE_NO(이케어번호) 기준</t>
+        </is>
+      </c>
     </row>
     <row r="641" ht="16" customHeight="1">
       <c r="A641" s="5" t="n">
